--- a/sampleprojects/SyntaxTests/excel/syntaxexample.xlsx
+++ b/sampleprojects/SyntaxTests/excel/syntaxexample.xlsx
@@ -597,7 +597,7 @@
     <t>set effectiveDate = the current date</t>
   </si>
   <si>
-    <t>set strBuffer = get current timestamp</t>
+    <t>set strBuffer = current time</t>
   </si>
   <si>
     <t>set street = using client (street)</t>

--- a/sampleprojects/SyntaxTests/excel/syntaxexample.xlsx
+++ b/sampleprojects/SyntaxTests/excel/syntaxexample.xlsx
@@ -266,10 +266,10 @@
     <t>set birthday = dateofBirth</t>
   </si>
   <si>
-    <t>set zip = $unknown</t>
-  </si>
-  <si>
-    <t>set pregnant = $unknown</t>
+    <t>set zip = the name "unknown"</t>
+  </si>
+  <si>
+    <t>set pregnant = the name "unknown"</t>
   </si>
   <si>
     <t>set effectivedate = currentdate</t>
@@ -290,7 +290,7 @@
     <t>perform syntax_examples_2</t>
   </si>
   <si>
-    <t>// perform $something -- the `perform $&lt;name&gt;` form parses but has no emitter, so it compiles to nothing and the table will not load. Use `perform table named (&lt;string expression&gt;)` for a dynamic table reference.</t>
+    <t>// perform $something -- the `$name` notation was removed (#1280); for a table chosen at runtime use `perform table named (&lt;string&gt;) among ...`</t>
   </si>
   <si>
     <t>add cases to clients</t>
@@ -347,7 +347,7 @@
     <t>remove each client from clients where age &lt; 18</t>
   </si>
   <si>
-    <t>remove $steve from clients array</t>
+    <t>remove the name "steve" from clients array</t>
   </si>
   <si>
     <t>remove importantDates from InterestingDates array</t>
@@ -362,10 +362,10 @@
     <t>clear clients</t>
   </si>
   <si>
-    <t>sort clients in ascending order by $steve</t>
-  </si>
-  <si>
-    <t>sort clients in descending order by $steve</t>
+    <t>sort clients in ascending order by the name "steve"</t>
+  </si>
+  <si>
+    <t>sort clients in descending order by the name "steve"</t>
   </si>
   <si>
     <t>Set InterestingClients = job's clients</t>
@@ -386,7 +386,7 @@
     <t>set errorCodes = [ 1 , 2, 3, 4 ]</t>
   </si>
   <si>
-    <t>set errorCodes = array of values [ job, cases, "clients", 10, -0.5, $boy ]</t>
+    <t>set errorCodes = array of values [ job, cases, "clients", 10, -0.5, the name "boy" ]</t>
   </si>
   <si>
     <t>set errorcodes = tokenize errorType by location</t>
@@ -404,7 +404,7 @@
     <t>set InterestingClients = job's clients</t>
   </si>
   <si>
-    <t>set client = new $theClient entity</t>
+    <t>set client = new client entity</t>
   </si>
   <si>
     <t>set client  = new client entity</t>
@@ -567,7 +567,7 @@
     <t>set tips = tips + 35.50</t>
   </si>
   <si>
-    <t>set street = street + $Oak</t>
+    <t>set street = street + the name "Oak"</t>
   </si>
   <si>
     <t>set street = street + billingAddress</t>
@@ -801,7 +801,7 @@
     <t>set eligible = clients includes case</t>
   </si>
   <si>
-    <t>set applying = there is match for all clients to $applying in cases</t>
+    <t>set applying = there is match for all clients to the name "applying" in cases</t>
   </si>
   <si>
     <t>set eligible = there is client where FPL_base &lt;867</t>
@@ -891,16 +891,16 @@
     <t>set eligible = totalIncome less than or equal to totalGroupIncome</t>
   </si>
   <si>
-    <t>set eligible = $aName is equal to $anotherName</t>
-  </si>
-  <si>
-    <t>set eligible = $aName equal to program</t>
-  </si>
-  <si>
-    <t>set eligible = $aName != $anotherName</t>
-  </si>
-  <si>
-    <t>set eligible = $aName != program</t>
+    <t>set eligible = the name "aName" is equal to the name "anotherName"</t>
+  </si>
+  <si>
+    <t>set eligible = the name "aName" equal to program</t>
+  </si>
+  <si>
+    <t>set eligible = the name "aName" != the name "anotherName"</t>
+  </si>
+  <si>
+    <t>set eligible = the name "aName" != program</t>
   </si>
   <si>
     <t>set eligible = program == programLevel</t>
@@ -1040,7 +1040,7 @@
     <t>TABLE_NUMBER: 800</t>
   </si>
   <si>
-    <t>// perform $something -- see Syntax_Examples_2; use `perform table named (&lt;string expression&gt;)`.</t>
+    <t>// perform $something -- see Syntax_Examples_2; the `$name` notation was removed (#1280); use `perform table named (&lt;string&gt;) among ...`</t>
   </si>
   <si>
     <t>//does effectiveDate == (1 months) ?</t>
